--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_05_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_05_20_Cau.xlsx
@@ -679,7 +679,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -693,7 +697,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Placeholder rỗng không tính xe.</t>
+          <t>Dung lượng fleet num_vehicles=2. Solution có cấu trúc `[[], [1,2], [], [3]]`. Các mảng rỗng `[]` là placeholder; chỉ có hai route không rỗng là `[1,2]` và `[3]` đại diện cho 2 xe thực sự được sử dụng.</t>
         </is>
       </c>
     </row>
@@ -963,7 +967,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So từng dimension trước, chỉ kết luận overall nếu objective được khai báo.</t>
+          <t>So sánh hai lời giải đa mục tiêu khi chưa biết trọng số: (a) B có tổng quãng đường tốt hơn (90 &lt; 100), (b) A dùng ít xe hơn (2 &lt; 3) và trễ giờ ít hơn (5 &lt; 12), (c) không thể kết luận giải pháp nào tối ưu tổng thể nếu chưa có trọng số chính thức, (e) hai lời giải ngang nhau về làm thêm giờ (0) và đơn hàng chưa phục vụ (0).</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1135,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -1145,7 +1153,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính ratio trước rồi áp cap; invalid/missing mới nhận zero.</t>
+          <t>Raw score = 100 * (reference cost / team cost) = 100 * (120 / 60) = 200. Áp dụng trần cap=150: min(150, 200) = 150 điểm.</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1171,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
@@ -1177,7 +1189,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cap chỉ tác động khi raw ratio vượt 150.</t>
+          <t>Raw score = 100 * (reference cost / team cost) = 100 * (80 / 100) = 80. Áp dụng cap=150: min(150, 80) = 80 điểm.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1207,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1209,7 +1225,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Score 100 nghĩa bằng reference cost.</t>
+          <t>Score = min(150, 100 * reference / team) = min(150, 100 * (100 / 200)) = min(150, 50) = 50 điểm.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1243,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
@@ -1241,7 +1261,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ lấy private instance theo contract.</t>
+          <t>Điểm chính thức xếp hạng chỉ tính trên các private instance theo quy định: (120 + 90 + 150) / 3 = 360 / 3 = 120 điểm.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1279,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -1273,7 +1297,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số gồm toàn bộ private instance bắt buộc.</t>
+          <t>Điểm trung bình private của cả 4 instances bắt buộc (kể cả instance thiếu bị 0 điểm): (150 + 110 + 0 + 90) / 4 = 350 / 4 = 87,5 điểm.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_05_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_05_20_Cau.xlsx
@@ -624,10 +624,25 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Normalization không được tự chèn order bị bỏ.
-Phân tích theo nguyên lý thiết kế: Normalization không được tự chèn order bị bỏ.</t>
+- 1.0 điểm: Phân tích đúng bản chất các route rỗng biểu thị xe không điều động và bảo toàn thứ tự thăm viếng [5, 2].
+- 1.0 điểm: Chuẩn hóa ngữ nghĩa danh sách xe mà không làm thay đổi thứ tự tương đối của các route và stops.
+- 1.0 điểm: Khẳng định nguyên tắc cấm tự ý chèn đơn hàng 7 vào các lộ trình trong quá trình chuẩn hóa.
+- 1.0 điểm: Ghi nhận chính xác đơn hàng 7 vào tập unserved_orders để bàn giao cho bộ phận đánh giá tính điểm phạt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Quy trình Chuẩn hóa Ngữ nghĩa Route List (Normalization Semantics):
+1. Phân tích hiện trạng input `[[], [5, 2], []]`:
+- Input chứa 3 routes đại diện cho đội xe 3 chiếc; trong đó Route 0 và Route 2 là danh sách rỗng `[]` (xe nhàn rỗi / unused vehicle), Route 1 phục vụ đơn 5 rồi đến đơn 2.
+- Đơn hàng hợp lệ số 7 có trong instance nhưng không xuất hiện trong bất kỳ route nào.
+2. Chuẩn hóa Ngữ nghĩa Route mà không đổi thứ tự:
+- Bảo toàn danh tính xe (Vehicle Index Integrity): Giữ nguyên cấu trúc mapping tương ứng với xe hoạt động: Route 1 giữ nguyên thứ tự thăm viếng `[5, 2]`. Nếu schema yêu cầu active routes only, normalize thành `[{'vehicle_id': 1, 'stops': [5, 2]}]` nhưng không được hoán đổi thứ tự của 5 và 2.
+3. Xử lý Order 7 bị bỏ quên:
+- Nguyên tắc bất biến: Normalization tuyệt đối KHÔNG ĐƯỢC tự ý chèn order 7 vào bất kỳ route rỗng hay route hiện tại nào (no synthetic order insertion).
+- Đơn hàng 7 phải được ghi nhận rõ ràng vào tập `unserved_orders = [7]`.
+- Lời giải giữ nguyên tính trung thực so với bài nộp; việc thiếu đơn hàng 7 sẽ được chuyển cho tầng evaluator để tính điểm phạt (unserved penalty) hoặc đánh giá mức độ hoàn thiện của lời giải.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Giai đoạn chuẩn hóa dữ liệu lộ trình chỉ chuyển đổi biểu diễn ngữ nghĩa của cấu trúc danh sách, tuyệt đối không được can thiệp vào logic nghiệp vụ bằng cách tự ý chèn các đơn hàng bị thiếu vào lời giải.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Geir Hasle et al., 'Geometric Modelling, Numerical Simulation, and Optimization: Industrial Mathematics at SINTEF', Chapter on VRP Data Models, Springer.</t>
         </is>
       </c>
     </row>
@@ -658,10 +673,29 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách ID lạ/trùng khỏi order có thật bị bỏ.
-Phân tích theo nguyên lý thiết kế: Tách ID lạ/trùng khỏi order có thật bị bỏ.</t>
+- 1.0 điểm: Báo cáo chính xác lỗi trùng lặp của order 2 kèm vị trí cụ thể (R1 index 1 và R2 index 1).
+- 1.0 điểm: Báo cáo chính xác lỗi đơn hàng lạ của order 9 tại R2 index 2.
+- 1.0 điểm: Báo cáo chính xác lỗi đơn hàng bị bỏ quên của order 4.
+- 1.0 điểm: Tách biệt rõ ràng 3 danh mục vi phạm (Duplicate, Alien, Missing) theo cấu trúc báo cáo chặt chẽ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Báo cáo Toàn bộ Vi phạm Danh tính Đơn hàng (Order Identity Integrity Violations):
+Tập đơn hàng hợp lệ của instance: S_true = {1, 2, 3, 4}.
+Lời giải đề xuất: R1 = [1, 2], R2 = [3, 2, 9].
+1. Vi phạm Đơn hàng Trùng lặp (Duplicate Order Violation):
+- Order ID `2` xuất hiện 2 lần trong lời giải:
+  + Vị trí 1: Route `R1`, chỉ số `index 1` (stop thứ 2 của R1).
+  + Vị trí 2: Route `R2`, chỉ số `index 1` (stop thứ 2 của R2).
+- Vi phạm quy tắc bất biến: Mỗi khách hàng chỉ được một xe duy nhất phục vụ đúng một lần.
+2. Vi phạm Đơn hàng Lạ / Không Tồn tại (Alien / Unknown Order Violation):
+- Order ID `9` xuất hiện tại Route `R2`, chỉ số `index 2` (stop thứ 3 của R2).
+- Vi phạm: ID 9 không thuộc tập hợp đơn hàng hợp lệ S_true (9 ∉ {1, 2, 3, 4}).
+3. Vi phạm Đơn hàng Bị Bỏ quên (Unserved / Missing Order Violation):
+- Order ID `4` thuộc S_true nhưng không xuất hiện ở bất kỳ route nào trong lời giải.
+Báo cáo cấu trúc: `{'duplicate_orders': [{'id': 2, 'occurrences': [('R1', 1), ('R2', 1)]}], 'alien_orders': [{'id': 9, 'route': 'R2', 'index': 2}], 'unserved_orders': [4]}`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiểm tra tính toàn vẹn danh tính yêu cầu bóc tách rõ 3 nhóm lỗi độc lập: đơn hàng trùng lặp kèm vị trí cụ thể, đơn hàng lạ không có trong đề bài, và đơn hàng có thật bị bỏ sót.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+David L. Poole, Alan K. Mackworth, 'Artificial Intelligence: Foundations of Computational Agents', Chapter 4: Constraint Satisfaction Problems, Cambridge University Press.</t>
         </is>
       </c>
     </row>
@@ -776,10 +810,29 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Cộng demand theo route rồi so cùng capacity.
-Phân tích theo nguyên lý thiết kế: Cộng demand theo route rồi so cùng capacity.</t>
+- 1.0 điểm: Tính chính xác tổng tải trọng route R1: Load(R1) = 4 + 7 = 11.
+- 1.0 điểm: Chẩn đoán chính xác R1 bị quá tải (overload) 1 đơn vị so với giới hạn 10.
+- 1.0 điểm: Tính chính xác tổng tải trọng route R2: Load(R2) = 2 và khẳng định R2 hợp lệ với dư lượng 8 đơn vị.
+- 1.0 điểm: Đưa ra chẩn đoán tổng thể cho solution (infeasible nếu là ràng buộc cứng, hoặc tính phạt nếu là ràng buộc mềm).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Tính toán Tải trọng (Load) và Chẩn đoán Sức chứa (Capacity Diagnostic):
+1. Thông số đầu vào: Sức chứa tối đa của mỗi xe: C_max = 10. Nhu cầu đơn hàng: q(1) = 4, q(2) = 7, q(3) = 2.
+2. Tính toán tải trọng từng lộ trình:
+- Lộ trình 1 (R1 = [1, 2]):
+  + Tổng tải trọng: Load(R1) = q(1) + q(2) = 4 + 7 = 11 đơn vị.
+  + So sánh với sức chứa: 11 &gt; 10.
+  + Chẩn đoán R1: VI PHẠM TẢI TRỌNG (Capacity Overload). Mức vượt quá: Overload(R1) = 11 - 10 = 1 đơn vị.
+- Lộ trình 2 (R2 = [3]):
+  + Tổng tải trọng: Load(R2) = q(3) = 2 đơn vị.
+  + So sánh với sức chứa: 2 &lt;= 10.
+  + Chẩn đoán R2: HỢP LỆ (Capacity Feasible). Dư lượng tải trọng (Slack): 10 - 2 = 8 đơn vị.
+3. Chẩn đoán Tổng thể Lời giải (Global Diagnostic):
+- Lời giải KHÔNG HỢP LỆ (INFEASIBLE) đối với bài toán chuẩn Capacitated VRP có ràng buộc cứng về tải trọng.
+- Nếu bài toán áp dụng hàm phạt mềm (soft capacity relaxation), R1 phát sinh chi phí phạt quá tải tương ứng với 1 đơn vị quá tải.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Tính tải trọng lộ trình bằng cách cộng tổng nhu cầu của tất cả các đơn hàng được gán cho route đó, sau đó so sánh với capacity của phương tiện để xác định mức quá tải hoặc dư lượng sức chứa.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Christos H. Papadimitriou, Kenneth Steiglitz, 'Combinatorial Optimization: Algorithms and Complexity', Prentice-Hall, Chapter 15.</t>
         </is>
       </c>
     </row>
@@ -862,10 +915,26 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách validity verdict khỏi raw outcome report.
-Phân tích theo nguyên lý thiết kế: Tách validity verdict khỏi raw outcome report.</t>
+- 1.0 điểm: Phân biệt rõ ràng bản chất giữa Hard Constraint (capacity) và Soft Constraints (lateness, overtime).
+- 1.0 điểm: Khẳng định nguyên tắc kiến trúc: tách biệt Validity Verdict khỏi Raw Metrics Report.
+- 1.0 điểm: Xác định chính xác phán quyết bài nộp là INVALID/INFEASIBLE do vi phạm capacity.
+- 1.0 điểm: Nêu rõ hậu quả tính điểm (score consequence): không tính điểm hoặc bị loại khi vi phạm ràng buộc cứng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân loại Evaluator Outcome và Hậu quả Điểm số (Hard/Soft Boundary):
+1. Phân loại Outcome Report (Báo cáo đo lường thô):
+- Evaluator phải luôn ghi nhận khách quan toàn bộ các đại lượng thô: Capacity Overload (&gt; 0), Lateness = 20, Overtime = 5, Unserved Orders = 1.
+2. Phân định Ranh giới Hard vs Soft Constraints:
+- Ràng buộc cứng (Hard Constraints): Sức chứa xe (Capacity) là giới hạn vật lý không thể phá vỡ. Khi có capacity overload, bài giải vi phạm ràng buộc cứng.
+- Ràng buộc mềm (Soft Constraints): Lateness (20 đơn vị) và Overtime (5 đơn vị) là các ràng buộc dịch vụ/vận hành, được giải quyết bằng hàm phạt chi phí bổ sung.
+- Trạng thái đơn không phục vụ (Unserved Order): Thường được mô hình hóa bằng soft penalty rất lớn trong bài toán mở, hoặc hard constraint nếu đề bài bắt buộc 100% tỷ lệ hoàn thành.
+3. Phán quyết và Hậu quả Điểm số (Validity Verdict &amp; Score Consequence):
+- Verdict: Bài nộp bị phán quyết `INVALID` / `INFEASIBLE` do vi phạm ràng buộc cứng về capacity.
+- Điểm số chính thức: 0 điểm hoặc bị đánh dấu loại (Disqualified), không cộng điểm khoảng cách.
+- Nguyên tắc kiến trúc: Báo cáo thẩm định luôn trả về 2 phần độc lập: (a) `validity_verdict` = False kèm mã vi phạm cứng, và (b) `raw_metrics` để phục vụ chẩn đoán thuật toán.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống thẩm định tối ưu hóa, vi phạm ràng buộc cứng dẫn đến việc từ chối công nhận kết quả (infeasible verdict), trong khi các đại lượng mềm chỉ làm tăng chi phí phạt. Evaluator phải tách bạch kết luận hợp lệ khỏi báo cáo đo lường thô.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pascal Van Hentenryck, Laurent Michel, 'Constraint-Based Local Search', The MIT Press, Chapter 2: Modeling Combinatorial Problems.</t>
         </is>
       </c>
     </row>
@@ -998,10 +1067,29 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc đủ năm dimension ngăn kết luận distance-only.
-Phân tích theo nguyên lý thiết kế: Đọc đủ năm dimension ngăn kết luận distance-only.</t>
+- 1.0 điểm: So sánh đầy đủ và chi tiết cả 5 chiều chi phí giữa hai phương án A và B.
+- 1.0 điểm: Kết luận chính xác về mặt Pareto: Không ứng viên nào áp đảo ứng viên kia (non-dominated).
+- 1.0 điểm: Chỉ ra sai lầm nếu chỉ đánh giá dựa trên khoảng cách (distance-only bias).
+- 1.0 điểm: Phân tích sự phụ thuộc của xếp hạng vào trọng số ẩn và bản chất đánh đổi thực tế trong vận tải.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+So sánh Quan hệ Dominance và Trade-off trên 5 Chiều Chi phí khi Trọng số Ẩn:
+Hai ứng viên: A = (dist=80, veh=3, late=0, ot=0, unserved=4); B = (dist=90, veh=2, late=5, ot=0, unserved=0).
+1. Phân tích đối đầu trên từng chiều:
+- Chiều 1 (Distance): A tốt hơn B (80 &lt; 90, A tiết kiệm 10 đơn vị khoảng cách).
+- Chiều 2 (Vehicles): B tốt hơn A (2 &lt; 3, B tiết kiệm 1 xe).
+- Chiều 3 (Lateness): A tốt hơn B (0 &lt; 5, A không trễ hạn).
+- Chiều 4 (Overtime): A và B bằng nhau (0 = 0).
+- Chiều 5 (Unserved Demand): B tốt hơn A (0 &lt; 4, B phục vụ toàn bộ đơn, A bỏ 4 đơn vị demand).
+2. Kết luận về Quan hệ Dominance (Pareto Dominance):
+- Không có ứng viên nào áp đảo (dominate) ứng viên kia: A không áp đảo B và B không áp đảo A.
+- Cả A và B đều nằm trên đường biên Pareto (Pareto Frontier).
+3. Trade-off khi Trọng số Ẩn:
+- Sai lầm phổ biến là kết luận A tốt hơn B chỉ vì cự ly ngắn hơn (distance-only fallacy).
+- Trên thực tế, thứ hạng phụ thuộc hoàn toàn vào bộ trọng số bí mật (W = [w_d, w_v, w_l, w_ot, w_u]). Nếu chi phí thuê xe và phạt bỏ đơn lớn hơn chi phí cự ly (thường thấy trong thực tế), B sẽ có chi phí tổng thể thấp hơn A rất nhiều.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích đa mục tiêu đòi hỏi kiểm tra toàn bộ 5 chiều chi phí. Khi mỗi giải pháp đều có chiều vượt trội và chiều kém hơn, chúng tạo thành quan hệ đánh đổi Pareto; không thể xếp hạng nếu chưa xác định bộ trọng số cụ thể.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kalyanmoy Deb, 'Multi-Objective Optimization using Evolutionary Algorithms', John Wiley &amp; Sons, Chapter 2: Concepts of Multi-Objective Optimization.</t>
         </is>
       </c>
     </row>
@@ -1032,10 +1120,28 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giải bất phương trình hai working costs; không suy hidden score.
-Phân tích theo nguyên lý thiết kế: Giải bất phương trình hai working costs; không suy hidden score.</t>
+- 1.0 điểm: Thiết lập đúng phương trình chi phí cho cả hai ứng viên: C_A = 100 + 2w và C_B = 80 + 3w.
+- 1.0 điểm: Giải chính xác giá trị ngưỡng hòa vốn w* = 20.
+- 1.0 điểm: Nêu rõ điều kiện đảo chiều ưu tiên: B tốt hơn khi w &lt; 20, A tốt hơn khi w &gt; 20.
+- 1.0 điểm: Đưa ra Boundary Claim khoa học: từ chối suy đoán hidden score khi chưa biết giá trị chính thức của w.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Giải Bất phương trình Tìm Ngưỡng w Đảo chiều Ưu tiên và Tuyên bố Ranh giới:
+1. Thiết lập biểu thức Working Cost:
+Hàm chi phí: C = Distance + w * Vehicles.
+- Phương án A: C_A(w) = 100 + 2w.
+- Phương án B: C_B(w) = 80 + 3w.
+2. Tìm điểm hòa vốn (Breakeven Threshold):
+C_A(w) = C_B(w) &lt;=&gt; 100 + 2w = 80 + 3w &lt;=&gt; 3w - 2w = 100 - 80 &lt;=&gt; w = 20.
+3. Phân tích miền giá trị và Đảo chiều Ưu tiên (Preference Switch):
+- Trường hợp w &lt; 20: Ta có C_B(w) &lt; C_A(w). Ứng viên B được ưu tiên hơn A (khoảng cách ngắn hơn 20 đơn vị bù đắp được chi phí của 1 xe phát sinh).
+- Trường hợp w &gt; 20: Ta có C_A(w) &lt; C_B(w). Ứng viên A được ưu tiên hơn B (tiết kiệm được 1 xe bù đắp được 20 đơn vị cự ly chạy thêm).
+- Trường hợp w = 20: C_A(20) = C_B(20) = 140, hai ứng viên có chi phí làm việc tương đương nhau.
+4. Tuyên bố Ranh giới (Boundary Claim):
+- Ngưỡng đảo chiều là w* = 20. Ta chỉ có thể kết luận ưu tiên có điều kiện gắn với w. Vì w_official không được tiết lộ, tuyệt đối không được khẳng định ứng viên nào chắc chắn chiến thắng điểm số chính thức.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi tham số chi phí chính thức bị ẩn, nhóm phát triển phải thiết lập hàm chi phí giả định, giải phương trình tìm ngưỡng hòa vốn và đưa ra kết luận có điều kiện thay vì suy đoán cảm tính.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+David G. Luenberger, Yinyu Ye, 'Linear and Nonlinear Programming', Springer, Chapter 3: Sensitivity Analysis and Duality.</t>
         </is>
       </c>
     </row>
@@ -1066,10 +1172,33 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Working objective là comparator có provenance.
-Phân tích theo nguyên lý thiết kế: Working objective là comparator có provenance.</t>
+- 1.0 điểm: Thiết lập công thức và tính chính xác chi phí khi p = 5: C_A = 150, C_B = 170 -&gt; A xếp trên B.
+- 1.0 điểm: Tính chính xác chi phí khi p = 20: C_A = 210, C_B = 170 -&gt; B xếp trên A.
+- 1.0 điểm: Tìm chính xác điểm hòa vốn (breakeven threshold) tại p = 10.
+- 1.0 điểm: Giải thích rõ ràng ý nghĩa độ nhạy và vai trò của working objective như một comparator có provenance.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Tính toán Xếp hạng tại hai giá trị p và Phân tích Độ nhạy (Sensitivity Analysis):
+Công thức working cost: C = Distance + 15*Vehicles + 4*Lateness + p*Unserved.
+- Candidate A = (100, 2, 0, 4): C_A(p) = 100 + 15*2 + 4*0 + 4*p = 130 + 4p.
+- Candidate B = (120, 2, 5, 0): C_B(p) = 120 + 15*2 + 4*5 + 0*p = 120 + 30 + 20 = 170 (hằng số, không đổi theo p).
+1. Tính toán và Xếp hạng tại p = 5:
+- C_A(5) = 130 + 4*5 = 150.
+- C_B(5) = 170.
+- So sánh: 150 &lt; 170 =&gt; C_A(5) &lt; C_B(5).
+- Xếp hạng: A xếp trên B (A được chọn).
+2. Tính toán và Xếp hạng tại p = 20:
+- C_A(20) = 130 + 4*20 = 210.
+- C_B(20) = 170.
+- So sánh: 170 &lt; 210 =&gt; C_B(20) &lt; C_A(20).
+- Xếp hạng: B xếp trên A (B được chọn).
+3. Giải thích Độ nhạy (Sensitivity Explanation):
+- Điểm hòa vốn giữa hai ứng viên: 130 + 4p = 170 &lt;=&gt; 4p = 40 &lt;=&gt; p = 10.
+- Khi penalty phạt đơn unserved nhẹ (p &lt; 10), thuật toán chấp nhận bỏ 4 đơn vị nhu cầu để tiết kiệm 20 đơn vị cự ly và 5 đơn vị trễ hạn. Khi penalty nặng (p &gt; 10), việc bỏ đơn bị trừng phạt nghiêm khắc, khiến phương án B (giao hết hàng dù xa hơn) trở nên vượt trội.
+- Phân tích này khẳng định working cost là một comparator có nguồn gốc kiểm chứng (provenance), giúp đội ngũ nhận diện rõ ngưỡng rủi ro của từng giải pháp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích độ nhạy với tham số phạt đơn hàng chưa phục vụ (p) cho thấy sự thay đổi thứ hạng rõ rệt tại điểm hòa vốn p = 10, làm cơ sở đánh giá độ bền vững của chiến lược định tuyến khi tham số đánh giá thực tế biến động.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Frederick S. Hillier, Gerald J. Lieberman, 'Introduction to Operations Research', McGraw-Hill, Chapter on Sensitivity Analysis.</t>
         </is>
       </c>
     </row>
@@ -1380,10 +1509,34 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: First-fit phải có route iteration order rõ; feasibility timing vẫn cần validator riêng.
-Phân tích theo nguyên lý thiết kế: First-fit phải có route iteration order rõ; feasibility timing vẫn cần validator riêng.</t>
+- 1.0 điểm: Mô tả chính xác quy tắc duyệt First-fit theo thứ tự R1 rồi đến R2 cho danh sách đơn đã sắp xếp.
+- 1.0 điểm: Phân bổ đúng đơn A vào R1 (load 6) và đơn B vào R2 (load 5) khi R1 quá tải.
+- 1.0 điểm: Phân bổ đúng đơn C vào R1 vì R1 duyệt trước và tải trọng đạt đúng 10 (6 + 4 = 10).
+- 1.0 điểm: Báo cáo kết quả lộ trình cuối cùng (R1=[A, C], R2=[B], unserved=[]) và lưu ý về việc cần validator thời gian độc lập.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Dựng Feasible Baseline theo Quy tắc First-fit Heuristic:
+1. Thông số: Sức chứa xe C = 10. Đội xe gồm 2 xe (R1, R2). Danh sách đơn theo thứ tự due-date: A(d=6, due=3), B(d=5, due=4), C(d=4, due=5).
+2. Quy trình duyệt First-fit (ưu tiên thử R1 rồi đến R2, mở route mới khi cần):
+- Bước 1 (Xét đơn A, demand = 6):
+  + Thử đưa vào R1: Load(R1) hiện tại = 0. Load mới = 0 + 6 = 6 &lt;= 10 -&gt; Hợp lệ.
+  + Gán A vào R1: R1 = [A], Load(R1) = 6.
+- Bước 2 (Xét đơn B, demand = 5):
+  + Thử đưa vào R1: Load(R1) mới = 6 + 5 = 11 &gt; 10 -&gt; Quá tải R1.
+  + Chuyển sang duyệt R2: Load(R2) hiện tại = 0. Load mới = 0 + 5 = 5 &lt;= 10 -&gt; Hợp lệ.
+  + Mở xe 2 và gán B vào R2: R2 = [B], Load(R2) = 5.
+- Bước 3 (Xét đơn C, demand = 4):
+  + Áp dụng đúng quy tắc duyệt từ đầu (R1 rồi đến R2): Thử đưa vào R1.
+  + Load(R1) mới = 6 + 4 = 10 &lt;= 10 -&gt; Hoàn toàn thỏa mãn sức chứa của R1!
+  + Gán C vào R1: R1 = [A, C], Load(R1) = 10.
+3. Kết quả Baseline Lời giải:
+- R1 = [A, C] (tổng tải: 10/10).
+- R2 = [B] (tổng tải: 5/10).
+- Unserved Orders: [] (Không có đơn nào bị bỏ rơi, phục vụ đủ 100%).
+4. Lưu ý Thẩm định Thời gian (Timing Validation): First-fit ở trên chỉ đảm bảo ràng buộc tải trọng (capacity-feasible). Tính khả thi về mặt khung thời gian (time windows due 3, 4, 5) bắt buộc phải được chuyển qua module Time Window Propagation Validator độc lập để kiểm tra.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thuật toán First-fit heuristic duyệt tuần tự các tuyến từ R1 đến R2 cho từng đơn hàng theo thứ tự ưu tiên. Khi đơn C đến, vì R1 còn đủ 4 chỗ trống (6 + 4 = 10) nên C được xếp vào R1 thay vì R2.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Michael R. Garey, David S. Johnson, 'Computers and Intractability: A Guide to the Theory of NP-Completeness', Chapter on Bin Packing and First-Fit Heuristics, W. H. Freeman.</t>
         </is>
       </c>
     </row>
